--- a/Spell Check.xlsx
+++ b/Spell Check.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7656" windowHeight="10632"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7656" windowHeight="10632" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -81,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +112,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
     </font>
   </fonts>
   <fills count="4">
@@ -160,13 +167,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -658,4 +666,60 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>